--- a/plantilla-cotizacion.xlsx
+++ b/plantilla-cotizacion.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Valor UF Neto + IVA</t>
+          <t>Total UF Neto + IVA</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -754,7 +754,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. Puedes dejar vacías 'Total UF Útil', 'Total UF Terraza', 'Valor UF Neto + IVA' y 'Valor Prom UF/m2': el cotizador las calcula solo a partir de los m2 y el valor UF/m2.</t>
+          <t>5. Puedes dejar vacías 'Total UF Útil', 'Total UF Terraza', 'Total UF Neto + IVA' y 'Valor Prom UF/m2': el cotizador las calcula solo a partir de los m2 y el valor UF/m2.</t>
         </is>
       </c>
     </row>

--- a/plantilla-cotizacion.xlsx
+++ b/plantilla-cotizacion.xlsx
@@ -694,7 +694,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="A2:A50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Modelo no reconocido" error="Elige un modelo de la lista o escribe uno nuevo." type="list">
-      <formula1>"Lingue,Huingán,Peumo,Boldo,Huingán Familiar,Roble,Maitén,Coihue,Otro"</formula1>
+      <formula1>"Lingue,Huingán,Peumo,Boldo,Mañío,Roble,Maitén,Coihue,Otro"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
